--- a/Registro de tiempos por tarea - Kairos - NexTech.xlsx
+++ b/Registro de tiempos por tarea - Kairos - NexTech.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Fase Construcción Iteración 3" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Fase Construcción Iteración 2" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Hoja 4" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Fase Construcción Iteración 1" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Fase Elaboración Iteración 2" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Fase Construcción Iteración 3" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Fase Construcción Iteración 2" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Hoja 4" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Fase Construcción Iteración 1" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Fase Elaboración Iteración 2" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Fase Construcción Iteración 3'!$A$3:$K$29</definedName>
@@ -1731,6 +1731,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K29" displayName="Tabla_4" name="Tabla_4" id="1">
   <autoFilter ref="$A$3:$K$29">
